--- a/diluksha-perera-month2-data-dictionary.xlsx
+++ b/diluksha-perera-month2-data-dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\de-training\month2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1145610A-A85C-4A32-BC59-1539975C1CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0FC7F7A-EC3F-4FA0-AD1C-CF3B1ED0E9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-990" windowWidth="29040" windowHeight="15990" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-990" windowWidth="29040" windowHeight="15990" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,15 @@
     <sheet name="dim_store" sheetId="5" r:id="rId5"/>
     <sheet name="dim_promotion" sheetId="6" r:id="rId6"/>
     <sheet name="fact_sales" sheetId="7" r:id="rId7"/>
-    <sheet name="Legend" sheetId="8" r:id="rId8"/>
+    <sheet name="fact_inventory_snapshot" sheetId="9" r:id="rId8"/>
+    <sheet name="Legend" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="279">
   <si>
     <t>RetailCo Analytical Data Warehouse – Data Dictionary</t>
   </si>
@@ -110,6 +111,12 @@
     <t>Central fact table at the grain of one row per order line item. Contains all measurable sales metrics: quantity, revenue, cost, discount, profit, and tax.</t>
   </si>
   <si>
+    <t>fact_inventory_snapshot</t>
+  </si>
+  <si>
+    <t>Daily inventory snapshot fact table at the grain of one row per product per store per day. Captures qty_on_hand and reorder_point for inventory management and stock analysis.</t>
+  </si>
+  <si>
     <t>dim_date  –  Column Reference</t>
   </si>
   <si>
@@ -807,6 +814,57 @@
   </si>
   <si>
     <t>White</t>
+  </si>
+  <si>
+    <t>fact_inventory_snapshot  –  Column Reference</t>
+  </si>
+  <si>
+    <t>inventory_snapshot_key</t>
+  </si>
+  <si>
+    <t>Surrogate primary key. Auto-generated integer for each snapshot row.</t>
+  </si>
+  <si>
+    <t>staging.inventory</t>
+  </si>
+  <si>
+    <t>FK to dim_product (is_current=TRUE). Links snapshot to active product attributes.</t>
+  </si>
+  <si>
+    <t>FK to dim_store. Identifies which store this inventory snapshot belongs to.</t>
+  </si>
+  <si>
+    <t>CURRENT_DATE → YYYYMMDD</t>
+  </si>
+  <si>
+    <t>FK to dim_date. Represents the date this snapshot was taken. Enables fiscal calendar analysis on inventory.</t>
+  </si>
+  <si>
+    <t>qty_on_hand</t>
+  </si>
+  <si>
+    <t>quantity_on_hand</t>
+  </si>
+  <si>
+    <t>Number of units in stock at the time of the snapshot. Primary inventory measure.</t>
+  </si>
+  <si>
+    <t>reorder_point</t>
+  </si>
+  <si>
+    <t>Minimum stock threshold. When qty_on_hand falls below this value, restocking should be triggered.</t>
+  </si>
+  <si>
+    <t>last_restock_date</t>
+  </si>
+  <si>
+    <t>Date stock was last replenished. Used to calculate days since last restock and identify slow-moving inventory.</t>
+  </si>
+  <si>
+    <t>snapshot_date</t>
+  </si>
+  <si>
+    <t>Calendar date when this snapshot was taken. Redundant with date_key but provides direct DATE access without joining dim_date.</t>
   </si>
 </sst>
 </file>
@@ -909,7 +967,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1324,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1493,6 +1551,26 @@
       </c>
       <c r="F10" s="5" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2">
+        <v>11</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1521,7 +1599,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -1534,424 +1612,424 @@
     </row>
     <row r="2" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1979,7 +2057,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -1992,90 +2070,90 @@
     </row>
     <row r="2" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>100</v>
-      </c>
       <c r="I4" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -2083,24 +2161,24 @@
         <v>1</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
@@ -2108,47 +2186,47 @@
         <v>1</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
@@ -2156,24 +2234,24 @@
         <v>1</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
@@ -2181,24 +2259,24 @@
         <v>1</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
@@ -2206,70 +2284,70 @@
         <v>1</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
@@ -2277,24 +2355,24 @@
         <v>1</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
@@ -2302,24 +2380,24 @@
         <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
@@ -2327,24 +2405,24 @@
         <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
@@ -2352,13 +2430,13 @@
         <v>1</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2386,7 +2464,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -2399,90 +2477,90 @@
     </row>
     <row r="2" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -2490,24 +2568,24 @@
         <v>1</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
@@ -2515,24 +2593,24 @@
         <v>1</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
@@ -2540,24 +2618,24 @@
         <v>1</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
@@ -2565,24 +2643,24 @@
         <v>1</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
@@ -2590,24 +2668,24 @@
         <v>1</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
@@ -2615,24 +2693,24 @@
         <v>1</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
@@ -2640,24 +2718,24 @@
         <v>1</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
@@ -2665,24 +2743,24 @@
         <v>1</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
@@ -2690,24 +2768,24 @@
         <v>1</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
@@ -2715,24 +2793,24 @@
         <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
@@ -2740,24 +2818,24 @@
         <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
@@ -2765,13 +2843,13 @@
         <v>1</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2799,7 +2877,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -2812,240 +2890,240 @@
     </row>
     <row r="2" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -3073,7 +3151,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -3086,217 +3164,217 @@
     </row>
     <row r="2" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -3324,7 +3402,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -3337,388 +3415,388 @@
     </row>
     <row r="2" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -3730,6 +3808,263 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="5" width="6" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+    </row>
+    <row r="2" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>278</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3741,64 +4076,64 @@
   <sheetData>
     <row r="1" spans="1:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
     </row>
     <row r="3" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
